--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
+++ b/StructureDefinition-dk-core-d-ecpr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
